--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_4.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_1_4.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HSbank_branches20201013\tams-svreport-parent\tams-svreport\src\main\resources\tpl\pbc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7770"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
   </bookViews>
   <sheets>
     <sheet name="表1-4境内募集余额分地区" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -34,9 +39,6 @@
     <t>产品品种：</t>
   </si>
   <si>
-    <t>单位：万元</t>
-  </si>
-  <si>
     <t>列编号</t>
   </si>
   <si>
@@ -1173,6 +1175,10 @@
   </si>
   <si>
     <t>${report.enddate}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：万元</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1183,9 +1189,9 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="179" formatCode="#,##0.000000_ "/>
+    <numFmt numFmtId="178" formatCode="#,##0.000000_ "/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1197,27 +1203,32 @@
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1229,12 +1240,14 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1247,7 +1260,16 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1354,7 +1376,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1439,7 +1461,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1490,7 +1512,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1511,10 +1533,13 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1528,6 +1553,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1788,7 +1816,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1827,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="7"/>
@@ -1840,14 +1868,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C3" s="51" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="52"/>
       <c r="E3" s="53" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F3" s="53"/>
       <c r="G3" s="52" t="s">
@@ -1855,7 +1883,7 @@
       </c>
       <c r="H3" s="51"/>
       <c r="I3" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="24.95" customHeight="1" thickBot="1">
@@ -1863,1150 +1891,1150 @@
         <v>5</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C4" s="42"/>
       <c r="D4" s="43"/>
       <c r="E4" s="44"/>
       <c r="F4" s="44"/>
       <c r="G4" s="54" t="s">
-        <v>6</v>
+        <v>368</v>
       </c>
       <c r="H4" s="55"/>
-      <c r="I4" s="54"/>
+      <c r="I4" s="56"/>
     </row>
     <row r="5" spans="1:9" s="12" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A5" s="35"/>
       <c r="B5" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="D5" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="E5" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="F5" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="G5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="H5" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="I5" s="39" t="s">
         <v>13</v>
-      </c>
-      <c r="I5" s="39" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="16" customFormat="1" ht="38.25" customHeight="1">
       <c r="A6" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="E6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="F6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="G6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="H6" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="I6" s="15" t="s">
         <v>22</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="18" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A7" s="33" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A8" s="33" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A9" s="33" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A10" s="33" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A11" s="33" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I11" s="30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A12" s="33" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G12" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I12" s="30" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="33" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G13" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H13" s="30" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I13" s="30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A14" s="33" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G14" s="30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I14" s="30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A15" s="33" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G15" s="30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H15" s="30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="22" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A16" s="33" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H16" s="30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I16" s="30" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A17" s="33" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G17" s="30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H17" s="30" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A18" s="33" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G18" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I18" s="30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A19" s="33" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G19" s="30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H19" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I19" s="30" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A20" s="33" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I20" s="30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A21" s="33" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G21" s="30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H21" s="30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I21" s="30" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A22" s="33" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G22" s="30" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I22" s="30" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A23" s="33" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G23" s="30" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H23" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I23" s="30" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A24" s="33" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G24" s="30" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H24" s="30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I24" s="30" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A25" s="33" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F25" s="30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G25" s="30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H25" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I25" s="30" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A26" s="33" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G26" s="30" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H26" s="30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I26" s="30" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A27" s="33" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F27" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G27" s="30" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H27" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I27" s="30" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A28" s="33" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G28" s="30" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H28" s="30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I28" s="30" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A29" s="33" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G29" s="30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H29" s="30" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I29" s="30" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A30" s="33" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E30" s="30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G30" s="30" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H30" s="30" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I30" s="30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A31" s="33" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G31" s="30" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I31" s="30" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A32" s="33" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E32" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G32" s="30" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H32" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I32" s="30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A33" s="33" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E33" s="30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G33" s="30" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H33" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I33" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A34" s="33" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G34" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H34" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I34" s="30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A35" s="33" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D35" s="30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E35" s="30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G35" s="30" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H35" s="30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I35" s="30" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A36" s="33" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D36" s="30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E36" s="30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G36" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H36" s="30" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I36" s="30" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A37" s="33" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C37" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D37" s="30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E37" s="30" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G37" s="30" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H37" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A38" s="33" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E38" s="30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G38" s="30" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H38" s="30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I38" s="30" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A39" s="33" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D39" s="30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E39" s="30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G39" s="30" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H39" s="30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I39" s="30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A40" s="33" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G40" s="30" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I40" s="30" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="41" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A41" s="33" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D41" s="30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E41" s="30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G41" s="30" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H41" s="30" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I41" s="30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A42" s="33" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D42" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E42" s="30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G42" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H42" s="30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I42" s="30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="20" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1">
       <c r="A43" s="45" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B43" s="46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C43" s="47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D43" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E43" s="47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F43" s="47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G43" s="47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H43" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I43" s="47" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="62.25" customHeight="1">
       <c r="A44" s="48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" s="48"/>
       <c r="C44" s="48"/>
@@ -3019,25 +3047,25 @@
     </row>
     <row r="45" spans="1:9" s="9" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A45" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="24" t="s">
+        <v>325</v>
+      </c>
+      <c r="C45" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B45" s="24" t="s">
-        <v>326</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>63</v>
-      </c>
       <c r="D45" s="23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E45" s="26"/>
       <c r="F45" s="23"/>
       <c r="G45" s="27"/>
       <c r="H45" s="28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
